--- a/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940AF31E-6AD2-F249-98B2-260B852C4C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85F9C95-C832-BD48-B9AD-7E013486E7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36860" yWindow="660" windowWidth="51160" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -59,10 +59,10 @@
     <t>Planned to be removed</t>
   </si>
   <si>
-    <t>Removal Date</t>
-  </si>
-  <si>
     <t>Element</t>
+  </si>
+  <si>
+    <t>Go Live Date</t>
   </si>
 </sst>
 </file>
@@ -246,7 +246,7 @@
     <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Deprecated since" dataDxfId="2"/>
     <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Planned to be removed" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Removal Date" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -582,7 +582,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">

--- a/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85F9C95-C832-BD48-B9AD-7E013486E7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F86C1F-6223-F64F-A4D0-35E5FD2A7F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36860" yWindow="660" windowWidth="51160" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Package</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Go Live Date</t>
+  </si>
+  <si>
+    <t>End of Compatibility Phase</t>
   </si>
 </sst>
 </file>
@@ -131,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -165,12 +168,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -196,6 +205,13 @@
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
@@ -211,13 +227,6 @@
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -236,17 +245,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
-  <autoFilter ref="A1:H1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Property / Operation" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{5A67E0BD-2295-9F48-B6C2-59EBC6AF29B1}" name="HTTP Header" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Deprecated since" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Planned to be removed" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live Date" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10">
+  <autoFilter ref="A1:I1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Property / Operation" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{5A67E0BD-2295-9F48-B6C2-59EBC6AF29B1}" name="HTTP Header" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Deprecated since" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Planned to be removed" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live Date" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{1180243E-59F0-9B46-8DAB-4E1A42982952}" name="End of Compatibility Phase" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -569,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.5" style="9" customWidth="1"/>
@@ -578,9 +588,10 @@
     <col min="5" max="5" width="60.33203125" style="9" customWidth="1"/>
     <col min="6" max="6" width="31.5" style="10" customWidth="1"/>
     <col min="7" max="8" width="31.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="26" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -605,8 +616,11 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="12" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>

--- a/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F86C1F-6223-F64F-A4D0-35E5FD2A7F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744F342E-5945-934C-96FA-7A7BC40B59FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36860" yWindow="660" windowWidth="51160" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -65,7 +65,7 @@
     <t>Go Live Date</t>
   </si>
   <si>
-    <t>End of Compatibility Phase</t>
+    <t>End of Compatibility Period</t>
   </si>
 </sst>
 </file>
@@ -207,13 +207,6 @@
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
@@ -227,6 +220,13 @@
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -245,7 +245,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
   <autoFilter ref="A1:I1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="8"/>
@@ -256,7 +256,7 @@
     <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Deprecated since" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Planned to be removed" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live Date" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{1180243E-59F0-9B46-8DAB-4E1A42982952}" name="End of Compatibility Phase" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{1180243E-59F0-9B46-8DAB-4E1A42982952}" name="End of Compatibility Period" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -588,7 +588,7 @@
     <col min="5" max="5" width="60.33203125" style="9" customWidth="1"/>
     <col min="6" max="6" width="31.5" style="10" customWidth="1"/>
     <col min="7" max="8" width="31.5" style="11" customWidth="1"/>
-    <col min="9" max="9" width="26" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.1640625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">

--- a/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
+++ b/jeaf-generator/src/main/resources/Deprecation_Report_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tillmann.schall/Projects/JEAF/jeaf-generator/jeaf-generator/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940AF31E-6AD2-F249-98B2-260B852C4C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744F342E-5945-934C-96FA-7A7BC40B59FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36860" yWindow="660" windowWidth="51160" windowHeight="28140" xr2:uid="{441949ED-3404-8548-92CD-A40A7EA6D1DC}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Package</t>
   </si>
@@ -59,10 +59,13 @@
     <t>Planned to be removed</t>
   </si>
   <si>
-    <t>Removal Date</t>
-  </si>
-  <si>
     <t>Element</t>
+  </si>
+  <si>
+    <t>Go Live Date</t>
+  </si>
+  <si>
+    <t>End of Compatibility Period</t>
   </si>
 </sst>
 </file>
@@ -131,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -165,12 +168,18 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <alignment vertical="top" textRotation="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -236,17 +245,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:H1048576" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8">
-  <autoFilter ref="A1:H1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Property / Operation" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{5A67E0BD-2295-9F48-B6C2-59EBC6AF29B1}" name="HTTP Header" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Deprecated since" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Planned to be removed" dataDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Removal Date" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}" name="Table1" displayName="Table1" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9">
+  <autoFilter ref="A1:I1048576" xr:uid="{5FC88E85-2BB1-CD48-A0D0-BB78642BF973}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A4DDCCBB-E133-DF45-8389-C4AD19D8AEB7}" name="Element" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{439690A4-77A7-D848-A33C-19AF8EF0CF49}" name="Package" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{BC971382-1AD8-4C4D-972D-DF92F8F0260A}" name="Property / Operation" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{5A67E0BD-2295-9F48-B6C2-59EBC6AF29B1}" name="HTTP Header" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1DDDD3D3-BC66-DB4E-A899-65EA0DA59605}" name="Description" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{122F67FD-2569-C44A-A432-EAFF5935108B}" name="Deprecated since" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4B86B03A-67C7-E347-8943-3AB848258236}" name="Planned to be removed" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E69C5988-012E-2C46-A6D4-42119249395E}" name="Go Live Date" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{1180243E-59F0-9B46-8DAB-4E1A42982952}" name="End of Compatibility Period" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -569,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E1136C3-A1B3-DD42-A00A-DCFCD8D149EA}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.5" style="9" customWidth="1"/>
@@ -578,11 +588,12 @@
     <col min="5" max="5" width="60.33203125" style="9" customWidth="1"/>
     <col min="6" max="6" width="31.5" style="10" customWidth="1"/>
     <col min="7" max="8" width="31.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="26.1640625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -603,10 +614,13 @@
         <v>5</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
